--- a/data/dimensions/dim_instituciones.xlsx
+++ b/data/dimensions/dim_instituciones.xlsx
@@ -32,12 +32,6 @@
     <t>caracter</t>
   </si>
   <si>
-    <t>departamento_id</t>
-  </si>
-  <si>
-    <t>municipio_id</t>
-  </si>
-  <si>
     <t>UNIVERSIDAD POPULAR DEL CESAR ( Principal)</t>
   </si>
   <si>
@@ -54,6 +48,12 @@
   </si>
   <si>
     <t>UNIVERSIDAD POPULAR DEL CESAR ( Seccional)</t>
+  </si>
+  <si>
+    <t>codigo_departamento</t>
+  </si>
+  <si>
+    <t>codigo_municipio</t>
   </si>
 </sst>
 </file>
@@ -376,16 +376,17 @@
   <cols>
     <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="55.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -394,10 +395,10 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -405,19 +406,19 @@
         <v>1120</v>
       </c>
       <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
       <c r="E2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>20001</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -425,19 +426,19 @@
         <v>1123</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>20011</v>
       </c>
     </row>
   </sheetData>
